--- a/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
+++ b/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -545,6 +545,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -618,6 +619,11 @@
           <t>Preferred Min OI</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Shortlist Max</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -659,20 +665,23 @@
       <c r="I2" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>200</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M2" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="N2" s="3" t="n">
+      <c r="M2" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N2" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -715,20 +724,23 @@
       <c r="I3" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <v>200</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M3" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="N3" s="3" t="n">
+      <c r="M3" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N3" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -771,20 +783,23 @@
       <c r="I4" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="J4" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K4" s="8" t="n">
+      <c r="J4" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="K4" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M4" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N4" s="6" t="n">
+      <c r="M4" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N4" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -827,20 +842,23 @@
       <c r="I5" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="J5" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K5" s="8" t="n">
+      <c r="J5" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="K5" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M5" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N5" s="6" t="n">
+      <c r="M5" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -880,23 +898,26 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M6" s="13" t="n">
+      <c r="M6" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="N6" s="13" t="n">
+      <c r="N6" s="7" t="n">
         <v>75</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -936,23 +957,26 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="N7" s="13" t="n">
+      <c r="N7" s="7" t="n">
         <v>75</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -995,20 +1019,23 @@
       <c r="I8" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="4" t="n">
         <v>200</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M8" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N8" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1051,20 +1078,23 @@
       <c r="I9" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="4" t="n">
         <v>200</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M9" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="N9" s="3" t="n">
+      <c r="M9" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N9" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1107,20 +1137,23 @@
       <c r="I10" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K10" s="8" t="n">
+      <c r="J10" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="K10" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N10" s="6" t="n">
+      <c r="M10" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N10" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1163,20 +1196,23 @@
       <c r="I11" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K11" s="8" t="n">
+      <c r="J11" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="K11" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N11" s="6" t="n">
+      <c r="M11" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N11" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1216,23 +1252,26 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="K12" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M12" s="13" t="n">
+      <c r="M12" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="N12" s="13" t="n">
+      <c r="N12" s="7" t="n">
         <v>75</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1272,34 +1311,37 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="K13" s="13" t="n">
+      <c r="K13" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="L13" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="M13" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="N13" s="13" t="n">
+      <c r="N13" s="7" t="n">
         <v>75</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PositionPlus_Baseline_Bullish</t>
+          <t>SemiAnnual_Baseline_Bullish</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>PositionPlus</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1314,14 +1356,14 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -1331,31 +1373,34 @@
       <c r="I14" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="4" t="n">
         <v>200</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="N14" s="3" t="n">
+      <c r="M14" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N14" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PositionPlus_Baseline_Bearish</t>
+          <t>SemiAnnual_Baseline_Bearish</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>PositionPlus</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1370,14 +1415,14 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -1387,31 +1432,34 @@
       <c r="I15" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="4" t="n">
         <v>200</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="N15" s="3" t="n">
+      <c r="M15" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N15" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>PositionPlus_Restrictive_Bullish</t>
+          <t>SemiAnnual_Restrictive_Bullish</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>PositionPlus</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1426,14 +1474,14 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -1443,31 +1491,34 @@
       <c r="I16" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="J16" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K16" s="8" t="n">
+      <c r="J16" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K16" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M16" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N16" s="6" t="n">
+      <c r="M16" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>PositionPlus_Restrictive_Bearish</t>
+          <t>SemiAnnual_Restrictive_Bearish</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>PositionPlus</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1482,14 +1533,14 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -1499,31 +1550,34 @@
       <c r="I17" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K17" s="8" t="n">
+      <c r="J17" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K17" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="M17" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N17" s="6" t="n">
+      <c r="M17" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N17" s="4" t="n">
         <v>1000</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>PositionPlus_Loose_Bullish</t>
+          <t>SemiAnnual_Loose_Bullish</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PositionPlus</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1538,48 +1592,51 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
           <t>SP500</t>
         </is>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="J18" s="13" t="n">
+      <c r="J18" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="K18" s="13" t="n">
+      <c r="K18" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M18" s="13" t="n">
+      <c r="M18" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="N18" s="13" t="n">
+      <c r="N18" s="7" t="n">
         <v>75</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PositionPlus_Loose_Bearish</t>
+          <t>SemiAnnual_Loose_Bearish</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>PositionPlus</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1594,37 +1651,40 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>SemiAnnual</t>
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
           <t>SP500</t>
         </is>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="K19" s="13" t="n">
+      <c r="K19" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M19" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="N19" s="13" t="n">
+      <c r="N19" s="7" t="n">
         <v>75</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1647,138 +1707,154 @@
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Bamendjou — 18 Options Search Profiles</t>
+          <t>Bamendjou - 18 Options Search Profiles (corrected 2026-09-29)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>3 horizon groups x 3 tiers x 2 directions = 18 profiles. Universe: SP500 (app default) for all 18. All are OPTIONS-mode profiles.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>3 horizon groups x 3 tiers x 2 directions = 18 profiles. Universe: SP500 (app default) for all 18.</t>
+          <t>Horizon groups</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Intraday       0-2 days hold   (DTE window 1-4)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Horizon groups</t>
+          <t xml:space="preserve">  Swing          5-15 days hold  (DTE window 10-30)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Intraday       0-2 days hold</t>
+          <t xml:space="preserve">  SemiAnnual     90-105 days hold (Semi-annual preset, DTE window 180-210). Replaced PositionPlus (Custom 15-200d) on</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Swing          5-15 days hold</t>
+          <t xml:space="preserve">                 2026-09-29: a 15-200d hold forces every contract past 200 DTE (it must outlive the max hold), so it never</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PositionPlus   15-200 days hold (Custom preset) -- collapses Position/Quarterly/SemiAnnual/Annual,</t>
+          <t xml:space="preserve">                 covered Position/Quarterly/Annual as this sheet used to claim. Same profile ids; a schedule built from an</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 which are identical on every execution parameter except hold-days.</t>
+          <t xml:space="preserve">                 old PositionPlus profile keeps its saved request until you open the profile and click Update.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Tiers</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Tiers</t>
+          <t xml:space="preserve">  Baseline       The app's own unmodified liquidity defaults. Freezes only the Settings block (scanSettings), like every profile.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Baseline       The app's own unmodified defaults for that horizon -- exactly what Reset to Defaults produces.</t>
+          <t xml:space="preserve">  Restrictive    Tighter liquidity/spread floor -- every contract it accepts, Baseline accepts too (before the shortlist cap).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Restrictive    Tighter liquidity/spread floor -- fewer, more liquid contracts pass the scan.</t>
+          <t xml:space="preserve">                 SemiAnnual_Restrictive keeps volume at the Baseline floor (50): a single ~200-DTE strike almost never trades</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Loose          Wider liquidity/spread floor -- more contracts pass the scan.</t>
+          <t xml:space="preserve">                 200/day (judgement from the measured Baseline run; a Restrictive run is not yet measured).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr"/>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 It still demands OI &gt;= 1000 and spread &lt;= 8%.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Filter columns</t>
+          <t xml:space="preserve">  Loose          Wider liquidity/spread floor -- more contracts pass. Shortlist cap raised to 20 so the cap does not hide them.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Max Bid/Ask Spread %      Hard-reject ceiling -- contract is dropped if its spread exceeds this.</t>
+          <t>Filter columns</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Min Volume                Hard-reject floor -- contract is dropped if volume is below this</t>
+          <t xml:space="preserve">  Max Bid/Ask Spread %      Hard-reject ceiling -- contract is dropped if its spread exceeds this.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">                             (unless volume=0 and OI clears Min Open Interest -- Tradier's off-hours sentinel).</t>
+          <t xml:space="preserve">  Min Volume                Hard-reject floor -- dropped if volume is below this</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Min Open Interest          Hard-reject floor -- contract is dropped if OI is below this.</t>
+          <t xml:space="preserve">                             (unless volume=0 and OI clears Min Open Interest -- Tradier's off-hours sentinel).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Preferred Spread Ceiling % Soft-rank threshold -- above this, the contract still passes but is scored</t>
+          <t xml:space="preserve">  Min Open Interest          Hard-reject floor -- dropped if OI is below this.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">                             down and flagged 'spread_elevated'.</t>
+          <t xml:space="preserve">  Preferred Spread Ceiling % Soft-rank threshold -- above this, scored down and flagged 'spread_elevated'.</t>
         </is>
       </c>
     </row>
@@ -1797,90 +1873,90 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr"/>
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                             Three soft flags on one contract reject it (too_many_soft_failures).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Bold orange cells</t>
+          <t xml:space="preserve">  Shortlist Max              How many ranked candidates the scan returns. NOTE: loading a profile writes this, the</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Mark a value this profile explicitly overrides. A plain (non-bold) cell is the horizon's own default,</t>
+          <t xml:space="preserve">                             fundamentals gate, spreads and confidence gate into Settings, and they stay there.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  not an override -- Baseline rows have none.</t>
+          <t>Bold orange cells</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr"/>
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mark a value this profile explicitly sets. A plain cell is the app default, not an override.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Why Restrictive shows no bold Preferred-* cells</t>
+          <t>Known behaviour (not changed here)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Restrictive's target Preferred values (200 / 1000 / 8%) are numerically identical to every horizon's</t>
+          <t xml:space="preserve">  Restrictive volume is the running session total: an early-morning scan sees less volume than a mid-day one.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  own default for those three fields. Raising just the hard floor to the same numbers already implies</t>
+          <t xml:space="preserve">  SemiAnnual uses Position scoring rules: an earnings date within 30 days rejects the stock (event_reject_days 30).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  clearing the (already-matching) soft floor, so no explicit override is needed -- confirmed live against</t>
+          <t xml:space="preserve">  Bearish profiles still reject debt/equity &gt;= 3 (fundamentals safety rule), which removes some natural shorts.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the running app. Loose's Preferred values genuinely differ from default, so those ARE overrides.</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr"/>
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mirrors docs/search-profiles/search-profiles-export.json (localStorage key bamendjou:search-profiles).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="A36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Exported from Bamendjou's client-side search-profile store (localStorage key bamendjou:search-profiles).</t>
-        </is>
-      </c>
+      <c r="A37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  These profiles have no backend sync and no in-app import/export -- this spreadsheet is a read-only mirror.</t>
-        </is>
-      </c>
+      <c r="A38" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
+++ b/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -546,6 +546,9 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -624,6 +627,21 @@
           <t>Shortlist Max</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Earnings Reject (d)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Earnings Caution (d)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Debt/Equity Reject</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -683,6 +701,15 @@
       <c r="O2" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -742,6 +769,15 @@
       <c r="O3" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -801,6 +837,15 @@
       <c r="O4" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -860,6 +905,15 @@
       <c r="O5" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -919,6 +973,15 @@
       <c r="O6" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="P6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -978,6 +1041,15 @@
       <c r="O7" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="P7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1037,6 +1109,15 @@
       <c r="O8" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P8" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1096,6 +1177,15 @@
       <c r="O9" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P9" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1155,6 +1245,15 @@
       <c r="O10" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P10" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1214,6 +1313,15 @@
       <c r="O11" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1273,6 +1381,15 @@
       <c r="O12" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="P12" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1332,6 +1449,15 @@
       <c r="O13" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="P13" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1391,6 +1517,15 @@
       <c r="O14" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P14" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1450,6 +1585,15 @@
       <c r="O15" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P15" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1509,6 +1653,15 @@
       <c r="O16" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P16" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1568,6 +1721,15 @@
       <c r="O17" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="P17" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -1627,6 +1789,15 @@
       <c r="O18" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="P18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -1685,6 +1856,15 @@
       </c>
       <c r="O19" s="7" t="n">
         <v>20</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1698,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1910,53 +2090,86 @@
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Known behaviour (not changed here)</t>
+          <t xml:space="preserve">  Earnings Reject / Caution  An earnings or ex-dividend date fewer than Reject days away grades the event rule REJECT,</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Restrictive volume is the running session total: an early-morning scan sees less volume than a mid-day one.</t>
+          <t xml:space="preserve">                             fewer than Caution days away CAUTION. It is a weighted part of the stock score, not a veto; Step 5 flags it.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SemiAnnual uses Position scoring rules: an earnings date within 30 days rejects the stock (event_reject_days 30).</t>
+          <t xml:space="preserve">                             SemiAnnual profiles use 7 / 30 (Position default 30 / 60): a 90-105d hold crosses an</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Bearish profiles still reject debt/equity &gt;= 3 (fundamentals safety rule), which removes some natural shorts.</t>
+          <t xml:space="preserve">                             earnings date anyway, so only entering in the last week before one is blocked.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t xml:space="preserve">  Debt/Equity Reject         Fundamentals safety rule. Bearish profiles use 10 (default 3; 10 is the Settings page</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">                             maximum): heavy debt is often part of a bearish case, and a put's loss is capped at the</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                             premium. Negative equity is still rejected. Intraday skips fundamentals entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                             Loading a profile writes this into Settings, where it stays until another profile loads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Known behaviour (not changed here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Restrictive volume is the running session total: scan after about 10:30 ET (16:30 German time) for stable results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Mirrors docs/search-profiles/search-profiles-export.json (localStorage key bamendjou:search-profiles).</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
+++ b/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>200</v>
@@ -752,7 +752,7 @@
         <v>0.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>200</v>
@@ -956,7 +956,7 @@
         <v>0.3</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>75</v>
@@ -1024,7 +1024,7 @@
         <v>0.3</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>75</v>
@@ -1092,7 +1092,7 @@
         <v>0.2</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>200</v>
@@ -1160,7 +1160,7 @@
         <v>0.2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>200</v>
@@ -1364,7 +1364,7 @@
         <v>0.3</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>75</v>
@@ -1432,7 +1432,7 @@
         <v>0.3</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>75</v>
@@ -1500,7 +1500,7 @@
         <v>0.2</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>200</v>
@@ -1568,7 +1568,7 @@
         <v>0.2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>200</v>
@@ -1772,7 +1772,7 @@
         <v>0.3</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>75</v>
@@ -1840,7 +1840,7 @@
         <v>0.3</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>75</v>
@@ -1887,7 +1887,7 @@
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Bamendjou - 18 Options Search Profiles (corrected 2026-09-29)</t>
+          <t>Bamendjou - 18 Options Search Profiles (corrected 2026-09-29; min volume default 0 from 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 SemiAnnual_Restrictive keeps volume at the Baseline floor (50): a single ~200-DTE strike almost never trades</t>
+          <t xml:space="preserve">                 SemiAnnual_Restrictive keeps an explicit volume floor of 50 (the Baseline floor is now 0, off): a single ~200-DTE strike almost never trades</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Min Volume                Hard-reject floor -- dropped if volume is below this</t>
+          <t xml:space="preserve">  Min Volume                Optional hard floor; 0 = off (the app default since 2026-10-02 -- volume is a soft rule). Above 0, dropped if volume is below this</t>
         </is>
       </c>
     </row>
@@ -2041,14 +2041,14 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Preferred Min Volume       Soft-rank threshold -- below this, scored down and flagged 'low_volume'.</t>
+          <t xml:space="preserve">  Preferred Min Volume       Soft-rank threshold -- below this, scored down and flagged 'thin_liquidity'.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Preferred Min OI           Soft-rank threshold -- below this, scored down and flagged 'low_open_interest'.</t>
+          <t xml:space="preserve">  Preferred Min OI           Soft-rank threshold -- below this, scored down and flagged 'thin_liquidity' (volume and open interest together count as one soft miss).</t>
         </is>
       </c>
     </row>

--- a/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
+++ b/docs/search-profiles/Bamendjou_Options_Search_Profiles.xlsx
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>200</v>
@@ -752,7 +752,7 @@
         <v>0.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>200</v>
@@ -956,7 +956,7 @@
         <v>0.3</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>75</v>
@@ -1024,7 +1024,7 @@
         <v>0.3</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>75</v>
@@ -1092,7 +1092,7 @@
         <v>0.2</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>200</v>
@@ -1160,7 +1160,7 @@
         <v>0.2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>200</v>
@@ -1364,7 +1364,7 @@
         <v>0.3</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>75</v>
@@ -1432,7 +1432,7 @@
         <v>0.3</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>75</v>
@@ -1500,7 +1500,7 @@
         <v>0.2</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>200</v>
@@ -1568,7 +1568,7 @@
         <v>0.2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>200</v>
@@ -1772,7 +1772,7 @@
         <v>0.3</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>75</v>
@@ -1840,7 +1840,7 @@
         <v>0.3</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>75</v>
@@ -1971,7 +1971,7 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 SemiAnnual_Restrictive keeps volume at the Baseline floor (50): a single ~200-DTE strike almost never trades</t>
+          <t xml:space="preserve">                 SemiAnnual_Restrictive keeps an explicit 50; the Baseline floor is now 0 (off): a single ~200-DTE strike almost never trades</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Min Volume                Hard-reject floor -- dropped if volume is below this</t>
+          <t xml:space="preserve">  Min Volume                Optional hard floor; 0 = off -- dropped if volume is below this</t>
         </is>
       </c>
     </row>
@@ -2041,14 +2041,14 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Preferred Min Volume       Soft-rank threshold -- below this, scored down and flagged 'low_volume'.</t>
+          <t xml:space="preserve">  Preferred Min Volume       Soft-rank threshold -- below this, scored down and flagged 'thin_liquidity' (volume and open interest together count as one soft miss).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Preferred Min OI           Soft-rank threshold -- below this, scored down and flagged 'low_open_interest'.</t>
+          <t xml:space="preserve">  Preferred Min OI           Soft-rank threshold -- below this, scored down and flagged 'thin_liquidity' (volume and open interest together count as one soft miss).</t>
         </is>
       </c>
     </row>
